--- a/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/1_fold/35.xlsx
+++ b/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/1_fold/35.xlsx
@@ -426,13 +426,13 @@
         <v>-7.425729853499868</v>
       </c>
       <c r="E2">
-        <v>-20.5383027084015</v>
+        <v>-29.95258128650247</v>
       </c>
       <c r="F2">
-        <v>-4.164407687869114</v>
+        <v>-4.705036703101794</v>
       </c>
       <c r="G2">
-        <v>-15.07933579404346</v>
+        <v>-19.33343481491726</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -449,13 +449,13 @@
         <v>-7.237996851724884</v>
       </c>
       <c r="E3">
-        <v>-21.17385592148201</v>
+        <v>-30.05401231156327</v>
       </c>
       <c r="F3">
-        <v>-4.085681306641854</v>
+        <v>-4.626042759203431</v>
       </c>
       <c r="G3">
-        <v>-14.2787200819172</v>
+        <v>-18.94087694596156</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -472,13 +472,13 @@
         <v>-7.101485590399037</v>
       </c>
       <c r="E4">
-        <v>-22.08778348876202</v>
+        <v>-30.21605696121674</v>
       </c>
       <c r="F4">
-        <v>-4.423303979205266</v>
+        <v>-4.5766778605684</v>
       </c>
       <c r="G4">
-        <v>-14.12258647792132</v>
+        <v>-18.55488719935578</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -495,13 +495,13 @@
         <v>-7.023754060409775</v>
       </c>
       <c r="E5">
-        <v>-22.37529630350901</v>
+        <v>-30.94646132662491</v>
       </c>
       <c r="F5">
-        <v>-4.040060628667478</v>
+        <v>-4.707137442835294</v>
       </c>
       <c r="G5">
-        <v>-13.62713354305954</v>
+        <v>-18.51111516623553</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -518,13 +518,13 @@
         <v>-6.983682539503122</v>
       </c>
       <c r="E6">
-        <v>-22.26607403891801</v>
+        <v>-30.56958134157355</v>
       </c>
       <c r="F6">
-        <v>-4.116074106650569</v>
+        <v>-4.525934558575111</v>
       </c>
       <c r="G6">
-        <v>-13.08036053124797</v>
+        <v>-18.40514460352346</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -541,13 +541,13 @@
         <v>-6.972747045339413</v>
       </c>
       <c r="E7">
-        <v>-23.42602001361274</v>
+        <v>-31.26882754157193</v>
       </c>
       <c r="F7">
-        <v>-4.001830644660878</v>
+        <v>-4.580165287334186</v>
       </c>
       <c r="G7">
-        <v>-13.42548490371699</v>
+        <v>-18.14965325153021</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -564,13 +564,13 @@
         <v>-6.97850726615919</v>
       </c>
       <c r="E8">
-        <v>-23.19922044988658</v>
+        <v>-31.97673671234699</v>
       </c>
       <c r="F8">
-        <v>-3.603812533126757</v>
+        <v>-4.608778754161686</v>
       </c>
       <c r="G8">
-        <v>-14.00035286024758</v>
+        <v>-18.14856739259333</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -587,13 +587,13 @@
         <v>-6.983966284573751</v>
       </c>
       <c r="E9">
-        <v>-24.64905668818232</v>
+        <v>-32.02153011299387</v>
       </c>
       <c r="F9">
-        <v>-3.83046213820673</v>
+        <v>-4.60851947516461</v>
       </c>
       <c r="G9">
-        <v>-13.77242676568707</v>
+        <v>-17.49547621078806</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -610,13 +610,13 @@
         <v>-6.97187221166323</v>
       </c>
       <c r="E10">
-        <v>-22.58457067282549</v>
+        <v>-32.63148386250901</v>
       </c>
       <c r="F10">
-        <v>-4.084303731650999</v>
+        <v>-4.487794038248013</v>
       </c>
       <c r="G10">
-        <v>-12.07494454042577</v>
+        <v>-17.28308154062504</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -633,13 +633,13 @@
         <v>-6.937148277956069</v>
       </c>
       <c r="E11">
-        <v>-25.45570923469464</v>
+        <v>-33.14965676507369</v>
       </c>
       <c r="F11">
-        <v>-4.191120879874592</v>
+        <v>-4.449455538111646</v>
       </c>
       <c r="G11">
-        <v>-13.19574959601927</v>
+        <v>-16.59332275642681</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -656,13 +656,13 @@
         <v>-6.870306784839082</v>
       </c>
       <c r="E12">
-        <v>-25.44917011822756</v>
+        <v>-33.32976776178077</v>
       </c>
       <c r="F12">
-        <v>-3.188539528592323</v>
+        <v>-4.53909317476858</v>
       </c>
       <c r="G12">
-        <v>-12.75663552514479</v>
+        <v>-16.2084354214856</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -679,13 +679,13 @@
         <v>-6.758870687174496</v>
       </c>
       <c r="E13">
-        <v>-26.16348707972347</v>
+        <v>-34.05754108379048</v>
       </c>
       <c r="F13">
-        <v>-3.425343261295812</v>
+        <v>-4.564840490382395</v>
       </c>
       <c r="G13">
-        <v>-11.48891507960952</v>
+        <v>-16.18525498161963</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -702,13 +702,13 @@
         <v>-6.608692288308711</v>
       </c>
       <c r="E14">
-        <v>-26.42444492288949</v>
+        <v>-34.33126922365812</v>
       </c>
       <c r="F14">
-        <v>-3.576897219474995</v>
+        <v>-4.449516837299454</v>
       </c>
       <c r="G14">
-        <v>-12.57414170229247</v>
+        <v>-16.02392547639986</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -725,13 +725,13 @@
         <v>-6.423501617715478</v>
       </c>
       <c r="E15">
-        <v>-27.07790825067033</v>
+        <v>-34.92504952825487</v>
       </c>
       <c r="F15">
-        <v>-3.445998602484618</v>
+        <v>-4.211845803925233</v>
       </c>
       <c r="G15">
-        <v>-11.87303105744008</v>
+        <v>-15.75260971672889</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -748,13 +748,13 @@
         <v>-6.206764202602156</v>
       </c>
       <c r="E16">
-        <v>-27.60873144537544</v>
+        <v>-35.39704105288933</v>
       </c>
       <c r="F16">
-        <v>-3.175892843453783</v>
+        <v>-4.445685638061506</v>
       </c>
       <c r="G16">
-        <v>-11.46184143818936</v>
+        <v>-15.29742956835234</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -771,13 +771,13 @@
         <v>-5.972030147753599</v>
       </c>
       <c r="E17">
-        <v>-28.72569314478936</v>
+        <v>-36.08342638670593</v>
       </c>
       <c r="F17">
-        <v>-3.341741109535675</v>
+        <v>-4.219760854458983</v>
       </c>
       <c r="G17">
-        <v>-10.74469451074474</v>
+        <v>-15.01075949847023</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -794,13 +794,13 @@
         <v>-5.737748057125525</v>
       </c>
       <c r="E18">
-        <v>-27.99368343534547</v>
+        <v>-36.15073762435594</v>
       </c>
       <c r="F18">
-        <v>-2.588643310791546</v>
+        <v>-4.237327213602748</v>
       </c>
       <c r="G18">
-        <v>-10.01462321351481</v>
+        <v>-14.73620933580739</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -817,13 +817,13 @@
         <v>-5.517665918677178</v>
       </c>
       <c r="E19">
-        <v>-27.62603021608474</v>
+        <v>-36.64339484012441</v>
       </c>
       <c r="F19">
-        <v>-3.24565877448496</v>
+        <v>-3.940166975196482</v>
       </c>
       <c r="G19">
-        <v>-10.57190058632248</v>
+        <v>-14.70566955320762</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -840,13 +840,13 @@
         <v>-5.320752003620179</v>
       </c>
       <c r="E20">
-        <v>-30.60847414058842</v>
+        <v>-37.36373920052453</v>
       </c>
       <c r="F20">
-        <v>-2.62258980695827</v>
+        <v>-4.067956729324154</v>
       </c>
       <c r="G20">
-        <v>-10.01731468703823</v>
+        <v>-14.48979715495559</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -863,13 +863,13 @@
         <v>-5.161025581800464</v>
       </c>
       <c r="E21">
-        <v>-30.9346510664129</v>
+        <v>-37.157381168469</v>
       </c>
       <c r="F21">
-        <v>-2.59169501630346</v>
+        <v>-3.731748908284724</v>
       </c>
       <c r="G21">
-        <v>-9.739487084291516</v>
+        <v>-14.446185683294</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -886,13 +886,13 @@
         <v>-5.039337770646008</v>
       </c>
       <c r="E22">
-        <v>-31.07130909077938</v>
+        <v>-38.75812653883335</v>
       </c>
       <c r="F22">
-        <v>-2.400622962806322</v>
+        <v>-3.783237740940533</v>
       </c>
       <c r="G22">
-        <v>-9.251794068173782</v>
+        <v>-14.45825924287572</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -909,13 +909,13 @@
         <v>-4.945628107077057</v>
       </c>
       <c r="E23">
-        <v>-30.55702614738728</v>
+        <v>-38.36301718166411</v>
       </c>
       <c r="F23">
-        <v>-2.114324277785563</v>
+        <v>-3.500639373108079</v>
       </c>
       <c r="G23">
-        <v>-9.171020067561104</v>
+        <v>-14.44479856471305</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -932,13 +932,13 @@
         <v>-4.877082749025431</v>
       </c>
       <c r="E24">
-        <v>-32.33252759394463</v>
+        <v>-38.64748006916694</v>
       </c>
       <c r="F24">
-        <v>-2.403773244039169</v>
+        <v>-3.473844172729723</v>
       </c>
       <c r="G24">
-        <v>-10.11185062545766</v>
+        <v>-14.11860885745589</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -955,13 +955,13 @@
         <v>-4.824595076676472</v>
       </c>
       <c r="E25">
-        <v>-32.63852337535393</v>
+        <v>-39.19040787489455</v>
       </c>
       <c r="F25">
-        <v>-2.340265628736142</v>
+        <v>-3.680109312761605</v>
       </c>
       <c r="G25">
-        <v>-8.974363730891778</v>
+        <v>-14.04202931804147</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -978,13 +978,13 @@
         <v>-4.774380133574465</v>
       </c>
       <c r="E26">
-        <v>-31.24786749962743</v>
+        <v>-39.26786742279576</v>
       </c>
       <c r="F26">
-        <v>-1.974633369181871</v>
+        <v>-3.594836343950021</v>
       </c>
       <c r="G26">
-        <v>-10.21011092760877</v>
+        <v>-14.47158584394406</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -1001,13 +1001,13 @@
         <v>-4.717527817285805</v>
       </c>
       <c r="E27">
-        <v>-32.45949241969769</v>
+        <v>-38.79610232186167</v>
       </c>
       <c r="F27">
-        <v>-1.941145788556298</v>
+        <v>-3.413786707659356</v>
       </c>
       <c r="G27">
-        <v>-8.796183548877124</v>
+        <v>-14.33746736778434</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -1024,13 +1024,13 @@
         <v>-4.650200974799027</v>
       </c>
       <c r="E28">
-        <v>-33.78439938130683</v>
+        <v>-39.56830903083465</v>
       </c>
       <c r="F28">
-        <v>-2.037210727891554</v>
+        <v>-3.552820720912628</v>
       </c>
       <c r="G28">
-        <v>-8.870184173316453</v>
+        <v>-14.43584850484763</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -1047,13 +1047,13 @@
         <v>-4.566414734146691</v>
       </c>
       <c r="E29">
-        <v>-32.4678836820339</v>
+        <v>-38.82723105219041</v>
       </c>
       <c r="F29">
-        <v>-1.953509172043081</v>
+        <v>-3.460885193080327</v>
       </c>
       <c r="G29">
-        <v>-8.649403891302457</v>
+        <v>-14.73615140126046</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -1070,13 +1070,13 @@
         <v>-4.45993792103262</v>
       </c>
       <c r="E30">
-        <v>-31.4342368474131</v>
+        <v>-38.89542534227191</v>
       </c>
       <c r="F30">
-        <v>-2.164796703638137</v>
+        <v>-3.446252911277277</v>
       </c>
       <c r="G30">
-        <v>-9.573807522233151</v>
+        <v>-14.37291172360054</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -1093,13 +1093,13 @@
         <v>-4.335151656709563</v>
       </c>
       <c r="E31">
-        <v>-32.01315243607967</v>
+        <v>-39.00222940174282</v>
       </c>
       <c r="F31">
-        <v>-1.860981361517779</v>
+        <v>-3.328075532491691</v>
       </c>
       <c r="G31">
-        <v>-10.17167880444337</v>
+        <v>-14.37114720282811</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -1116,13 +1116,13 @@
         <v>-4.192351109514902</v>
       </c>
       <c r="E32">
-        <v>-31.18950452661657</v>
+        <v>-38.59012694585979</v>
       </c>
       <c r="F32">
-        <v>-1.545880341901681</v>
+        <v>-3.405878284064829</v>
       </c>
       <c r="G32">
-        <v>-9.594339525667712</v>
+        <v>-14.82752742396265</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -1139,13 +1139,13 @@
         <v>-4.029999837114427</v>
       </c>
       <c r="E33">
-        <v>-30.80032973463439</v>
+        <v>-37.76831759684381</v>
       </c>
       <c r="F33">
-        <v>-1.71352699361505</v>
+        <v>-3.446200724130901</v>
       </c>
       <c r="G33">
-        <v>-9.625124288637394</v>
+        <v>-14.76697920132215</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -1162,13 +1162,13 @@
         <v>-3.854400574332812</v>
       </c>
       <c r="E34">
-        <v>-31.56417461635219</v>
+        <v>-38.03794746773451</v>
       </c>
       <c r="F34">
-        <v>-1.952309696043827</v>
+        <v>-3.364963561305756</v>
       </c>
       <c r="G34">
-        <v>-9.456736700327903</v>
+        <v>-14.75221582348977</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -1185,13 +1185,13 @@
         <v>-3.670977788645927</v>
       </c>
       <c r="E35">
-        <v>-30.0779385039828</v>
+        <v>-37.43867185992946</v>
       </c>
       <c r="F35">
-        <v>-1.929576809408801</v>
+        <v>-3.353719302180155</v>
       </c>
       <c r="G35">
-        <v>-10.62187327123778</v>
+        <v>-15.08583936075536</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -1208,13 +1208,13 @@
         <v>-3.482773805801728</v>
       </c>
       <c r="E36">
-        <v>-31.70117454050624</v>
+        <v>-37.06430064947834</v>
       </c>
       <c r="F36">
-        <v>-2.364923641215275</v>
+        <v>-3.355815071709238</v>
       </c>
       <c r="G36">
-        <v>-8.732875986529642</v>
+        <v>-14.93928647555014</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -1231,13 +1231,13 @@
         <v>-3.294551617210305</v>
       </c>
       <c r="E37">
-        <v>-29.46447745134871</v>
+        <v>-36.67852221300191</v>
       </c>
       <c r="F37">
-        <v>-1.876450294397657</v>
+        <v>-3.401684259904455</v>
       </c>
       <c r="G37">
-        <v>-10.14495939139591</v>
+        <v>-14.84483164549642</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -1254,13 +1254,13 @@
         <v>-3.113557147312335</v>
       </c>
       <c r="E38">
-        <v>-30.57717785672141</v>
+        <v>-36.25087577008756</v>
       </c>
       <c r="F38">
-        <v>-1.587424623886881</v>
+        <v>-3.354419272635521</v>
       </c>
       <c r="G38">
-        <v>-9.490835319382397</v>
+        <v>-15.25708229459247</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -1277,13 +1277,13 @@
         <v>-2.942014414321438</v>
       </c>
       <c r="E39">
-        <v>-29.06968055888601</v>
+        <v>-36.20795942191687</v>
       </c>
       <c r="F39">
-        <v>-1.862875009400579</v>
+        <v>-3.331564615992283</v>
       </c>
       <c r="G39">
-        <v>-9.812838841805149</v>
+        <v>-15.00109270549556</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -1300,13 +1300,13 @@
         <v>-2.778214941327284</v>
       </c>
       <c r="E40">
-        <v>-28.71899553173201</v>
+        <v>-35.55155711450504</v>
       </c>
       <c r="F40">
-        <v>-1.517415981206684</v>
+        <v>-3.236246864054352</v>
       </c>
       <c r="G40">
-        <v>-9.6205557357932</v>
+        <v>-14.97409851716834</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -1323,13 +1323,13 @@
         <v>-2.626567984075449</v>
       </c>
       <c r="E41">
-        <v>-27.62540075819767</v>
+        <v>-35.64175073131582</v>
       </c>
       <c r="F41">
-        <v>-2.106972517085718</v>
+        <v>-3.174026531695275</v>
       </c>
       <c r="G41">
-        <v>-9.430715812389233</v>
+        <v>-15.26733174358206</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -1346,13 +1346,13 @@
         <v>-2.486676800491295</v>
       </c>
       <c r="E42">
-        <v>-28.05085994816632</v>
+        <v>-35.51755506741846</v>
       </c>
       <c r="F42">
-        <v>-1.456140816054202</v>
+        <v>-3.374044953142647</v>
       </c>
       <c r="G42">
-        <v>-10.00842918281083</v>
+        <v>-15.42351831630656</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -1369,13 +1369,13 @@
         <v>-2.355710704032751</v>
       </c>
       <c r="E43">
-        <v>-26.54050518323207</v>
+        <v>-34.83271167900146</v>
       </c>
       <c r="F43">
-        <v>-1.859555741217561</v>
+        <v>-3.134213537581926</v>
       </c>
       <c r="G43">
-        <v>-10.12562580544657</v>
+        <v>-15.01506320767128</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -1392,13 +1392,13 @@
         <v>-2.235345584111386</v>
       </c>
       <c r="E44">
-        <v>-27.32993594309321</v>
+        <v>-34.00926075815769</v>
       </c>
       <c r="F44">
-        <v>-1.815666351115035</v>
+        <v>-3.336459438975425</v>
       </c>
       <c r="G44">
-        <v>-10.35551008769356</v>
+        <v>-15.30833616063147</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -1415,13 +1415,13 @@
         <v>-2.127206756140853</v>
       </c>
       <c r="E45">
-        <v>-26.20711439831337</v>
+        <v>-33.81788518235654</v>
       </c>
       <c r="F45">
-        <v>-1.715466201705004</v>
+        <v>-3.078211759315665</v>
       </c>
       <c r="G45">
-        <v>-9.746826563752082</v>
+        <v>-15.35373698215704</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -1438,13 +1438,13 @@
         <v>-2.031044474624118</v>
       </c>
       <c r="E46">
-        <v>-25.67969208758802</v>
+        <v>-33.76849990906589</v>
       </c>
       <c r="F46">
-        <v>-1.92621529448824</v>
+        <v>-3.013860037629185</v>
       </c>
       <c r="G46">
-        <v>-9.798126777428628</v>
+        <v>-15.3943027519225</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -1461,13 +1461,13 @@
         <v>-1.946840921180147</v>
       </c>
       <c r="E47">
-        <v>-24.9118802626395</v>
+        <v>-32.92220962956444</v>
       </c>
       <c r="F47">
-        <v>-1.832204706311927</v>
+        <v>-3.018651314686978</v>
       </c>
       <c r="G47">
-        <v>-9.99193604493418</v>
+        <v>-15.56426781518145</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -1484,13 +1484,13 @@
         <v>-1.878274081307408</v>
       </c>
       <c r="E48">
-        <v>-25.13838547555515</v>
+        <v>-32.72447607625652</v>
       </c>
       <c r="F48">
-        <v>-1.737594380135987</v>
+        <v>-3.136141976895643</v>
       </c>
       <c r="G48">
-        <v>-10.1287642026178</v>
+        <v>-15.82141278467157</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -1507,13 +1507,13 @@
         <v>-1.825919671073203</v>
       </c>
       <c r="E49">
-        <v>-24.34565345814242</v>
+        <v>-32.60842713709896</v>
       </c>
       <c r="F49">
-        <v>-1.648998829671774</v>
+        <v>-3.051437268122379</v>
       </c>
       <c r="G49">
-        <v>-10.00311244667476</v>
+        <v>-15.60508022058958</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -1530,13 +1530,13 @@
         <v>-1.787434098327585</v>
       </c>
       <c r="E50">
-        <v>-24.72304289651964</v>
+        <v>-31.65867028347025</v>
       </c>
       <c r="F50">
-        <v>-1.896674884537007</v>
+        <v>-3.067384168993672</v>
       </c>
       <c r="G50">
-        <v>-10.68399234773666</v>
+        <v>-15.74779121769649</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -1553,13 +1553,13 @@
         <v>-1.765558093367633</v>
       </c>
       <c r="E51">
-        <v>-24.89854390668691</v>
+        <v>-30.99582622178252</v>
       </c>
       <c r="F51">
-        <v>-1.152029746771045</v>
+        <v>-3.002497321964984</v>
       </c>
       <c r="G51">
-        <v>-11.30893727136704</v>
+        <v>-15.9679706356951</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -1576,13 +1576,13 @@
         <v>-1.761000959243506</v>
       </c>
       <c r="E52">
-        <v>-24.17418731831599</v>
+        <v>-31.07026980599462</v>
       </c>
       <c r="F52">
-        <v>-1.09323057178553</v>
+        <v>-2.989998086224143</v>
       </c>
       <c r="G52">
-        <v>-10.54872676754758</v>
+        <v>-16.20107938929734</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -1599,13 +1599,13 @@
         <v>-1.773067795568052</v>
       </c>
       <c r="E53">
-        <v>-22.32544686163258</v>
+        <v>-30.38275235367609</v>
       </c>
       <c r="F53">
-        <v>-1.390455422849215</v>
+        <v>-3.109886872063913</v>
       </c>
       <c r="G53">
-        <v>-11.10274987409016</v>
+        <v>-16.21189825211968</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -1622,13 +1622,13 @@
         <v>-1.803056071507499</v>
       </c>
       <c r="E54">
-        <v>-23.30422217670244</v>
+        <v>-30.48151837178338</v>
       </c>
       <c r="F54">
-        <v>-1.391006287172077</v>
+        <v>-2.993452378293817</v>
       </c>
       <c r="G54">
-        <v>-11.05239647643784</v>
+        <v>-15.93080976201678</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -1645,13 +1645,13 @@
         <v>-1.854253671405861</v>
       </c>
       <c r="E55">
-        <v>-23.05081329970721</v>
+        <v>-29.7163896676844</v>
       </c>
       <c r="F55">
-        <v>-2.18144771680181</v>
+        <v>-3.395406063358638</v>
       </c>
       <c r="G55">
-        <v>-10.87742752359628</v>
+        <v>-16.1454125660545</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -1668,13 +1668,13 @@
         <v>-1.927954144892738</v>
       </c>
       <c r="E56">
-        <v>-21.63214654800626</v>
+        <v>-29.78651308769318</v>
       </c>
       <c r="F56">
-        <v>-1.640307598881602</v>
+        <v>-3.065651224387016</v>
       </c>
       <c r="G56">
-        <v>-10.55744343395248</v>
+        <v>-16.13589640290186</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -1691,13 +1691,13 @@
         <v>-2.022187326699771</v>
       </c>
       <c r="E57">
-        <v>-22.81591682445534</v>
+        <v>-29.82565042430447</v>
       </c>
       <c r="F57">
-        <v>-1.864153180303098</v>
+        <v>-3.196754448125886</v>
       </c>
       <c r="G57">
-        <v>-11.32769151184702</v>
+        <v>-16.1744791558893</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -1714,13 +1714,13 @@
         <v>-2.140644273373754</v>
       </c>
       <c r="E58">
-        <v>-21.28160643202052</v>
+        <v>-29.09879411828132</v>
       </c>
       <c r="F58">
-        <v>-1.810817088339047</v>
+        <v>-3.044445018875349</v>
       </c>
       <c r="G58">
-        <v>-11.98745344291391</v>
+        <v>-16.11675648386657</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -1737,13 +1737,13 @@
         <v>-2.283139701625532</v>
       </c>
       <c r="E59">
-        <v>-21.9411152726016</v>
+        <v>-29.18932284216865</v>
       </c>
       <c r="F59">
-        <v>-1.772882831495246</v>
+        <v>-3.165179567833377</v>
       </c>
       <c r="G59">
-        <v>-11.34871016547585</v>
+        <v>-16.62057847785163</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -1760,13 +1760,13 @@
         <v>-2.444921754370789</v>
       </c>
       <c r="E60">
-        <v>-21.06704733353709</v>
+        <v>-29.22503891666715</v>
       </c>
       <c r="F60">
-        <v>-1.847452465095258</v>
+        <v>-3.258816562311027</v>
       </c>
       <c r="G60">
-        <v>-11.456878930426</v>
+        <v>-16.54619051958421</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -1783,13 +1783,13 @@
         <v>-2.624291089076848</v>
       </c>
       <c r="E61">
-        <v>-20.45925366612361</v>
+        <v>-28.98522451864295</v>
       </c>
       <c r="F61">
-        <v>-1.748841952731199</v>
+        <v>-3.084658114444251</v>
       </c>
       <c r="G61">
-        <v>-11.11800155738958</v>
+        <v>-16.50477559488793</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -1806,13 +1806,13 @@
         <v>-2.819127823499899</v>
       </c>
       <c r="E62">
-        <v>-19.45536343420721</v>
+        <v>-28.58988420929932</v>
       </c>
       <c r="F62">
-        <v>-2.025628494865612</v>
+        <v>-3.232232595620386</v>
       </c>
       <c r="G62">
-        <v>-11.07723549961899</v>
+        <v>-17.15156515325918</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -1829,13 +1829,13 @@
         <v>-3.024116401118855</v>
       </c>
       <c r="E63">
-        <v>-22.10974658769922</v>
+        <v>-28.9254441332677</v>
       </c>
       <c r="F63">
-        <v>-1.947037965892411</v>
+        <v>-3.054887418355039</v>
       </c>
       <c r="G63">
-        <v>-10.79169432576577</v>
+        <v>-16.59226834767255</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -1852,13 +1852,13 @@
         <v>-3.232691640785185</v>
       </c>
       <c r="E64">
-        <v>-20.0929725744872</v>
+        <v>-28.88503203122325</v>
       </c>
       <c r="F64">
-        <v>-2.131246167089951</v>
+        <v>-3.234412858624554</v>
       </c>
       <c r="G64">
-        <v>-11.88114189401129</v>
+        <v>-16.68745811883599</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -1875,13 +1875,13 @@
         <v>-3.442356125536963</v>
       </c>
       <c r="E65">
-        <v>-19.23441918737298</v>
+        <v>-28.04610052198426</v>
       </c>
       <c r="F65">
-        <v>-2.047282018774791</v>
+        <v>-3.17022846715344</v>
       </c>
       <c r="G65">
-        <v>-11.59660381545647</v>
+        <v>-16.66069566869652</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -1898,13 +1898,13 @@
         <v>-3.647889820716495</v>
       </c>
       <c r="E66">
-        <v>-21.73656863014913</v>
+        <v>-27.60663023343588</v>
       </c>
       <c r="F66">
-        <v>-2.050892872283594</v>
+        <v>-3.142058176886437</v>
       </c>
       <c r="G66">
-        <v>-11.81767542547793</v>
+        <v>-16.58402012346146</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -1921,13 +1921,13 @@
         <v>-3.840117679686715</v>
       </c>
       <c r="E67">
-        <v>-19.16462181749275</v>
+        <v>-28.29147588608988</v>
       </c>
       <c r="F67">
-        <v>-2.221493482155346</v>
+        <v>-3.236384373043216</v>
       </c>
       <c r="G67">
-        <v>-11.70623253098944</v>
+        <v>-16.47259709224621</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -1944,13 +1944,13 @@
         <v>-4.017088756272912</v>
       </c>
       <c r="E68">
-        <v>-21.09724319822024</v>
+        <v>-27.68641741697703</v>
       </c>
       <c r="F68">
-        <v>-1.807613791592421</v>
+        <v>-3.245814507556686</v>
       </c>
       <c r="G68">
-        <v>-11.46731708051132</v>
+        <v>-16.69724078090454</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -1967,13 +1967,13 @@
         <v>-4.174175123241357</v>
       </c>
       <c r="E69">
-        <v>-19.60502950016072</v>
+        <v>-28.01439667545656</v>
       </c>
       <c r="F69">
-        <v>-1.724742259881553</v>
+        <v>-3.128630341287057</v>
       </c>
       <c r="G69">
-        <v>-11.0664629844342</v>
+        <v>-17.02644142932966</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -1990,13 +1990,13 @@
         <v>-4.304013943295997</v>
       </c>
       <c r="E70">
-        <v>-19.92073659407946</v>
+        <v>-27.7094854635721</v>
       </c>
       <c r="F70">
-        <v>-2.550741360276455</v>
+        <v>-3.404870989303025</v>
       </c>
       <c r="G70">
-        <v>-12.59341900896765</v>
+        <v>-16.4829822736029</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -2013,13 +2013,13 @@
         <v>-4.403256405427824</v>
       </c>
       <c r="E71">
-        <v>-19.42257728239168</v>
+        <v>-28.01451441578076</v>
       </c>
       <c r="F71">
-        <v>-2.415949416492919</v>
+        <v>-3.137071405121584</v>
       </c>
       <c r="G71">
-        <v>-11.25465425615961</v>
+        <v>-16.61808563706056</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -2036,13 +2036,13 @@
         <v>-4.469739171905762</v>
       </c>
       <c r="E72">
-        <v>-20.58500938931661</v>
+        <v>-28.26350350214449</v>
       </c>
       <c r="F72">
-        <v>-2.268973016581606</v>
+        <v>-3.346266480657168</v>
       </c>
       <c r="G72">
-        <v>-10.80627396832072</v>
+        <v>-16.76630538194481</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -2059,13 +2059,13 @@
         <v>-4.498670527092044</v>
       </c>
       <c r="E73">
-        <v>-20.23934643983713</v>
+        <v>-27.75989190775148</v>
       </c>
       <c r="F73">
-        <v>-2.173424978505697</v>
+        <v>-3.658060657601291</v>
       </c>
       <c r="G73">
-        <v>-11.44503379848648</v>
+        <v>-16.5745105813999</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -2082,13 +2082,13 @@
         <v>-4.485637332482986</v>
       </c>
       <c r="E74">
-        <v>-19.12033787017175</v>
+        <v>-28.54193672650611</v>
       </c>
       <c r="F74">
-        <v>-2.290870080507208</v>
+        <v>-3.473227039014637</v>
       </c>
       <c r="G74">
-        <v>-11.49456618084506</v>
+        <v>-16.21479829001208</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -2105,13 +2105,13 @@
         <v>-4.430702824608873</v>
       </c>
       <c r="E75">
-        <v>-20.36580860497533</v>
+        <v>-28.60582443780632</v>
       </c>
       <c r="F75">
-        <v>-2.438619347205333</v>
+        <v>-3.36264496094532</v>
       </c>
       <c r="G75">
-        <v>-10.8553759797592</v>
+        <v>-16.33581362692737</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -2128,13 +2128,13 @@
         <v>-4.331914938825172</v>
       </c>
       <c r="E76">
-        <v>-21.9620775787831</v>
+        <v>-29.11427697091354</v>
       </c>
       <c r="F76">
-        <v>-2.068352372032399</v>
+        <v>-3.48216098145383</v>
       </c>
       <c r="G76">
-        <v>-11.24356723914859</v>
+        <v>-16.13191712716366</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -2151,13 +2151,13 @@
         <v>-4.185540321576432</v>
       </c>
       <c r="E77">
-        <v>-23.10527725659746</v>
+        <v>-28.55046384306255</v>
       </c>
       <c r="F77">
-        <v>-2.886725522117128</v>
+        <v>-3.651398926947977</v>
       </c>
       <c r="G77">
-        <v>-11.76257801606784</v>
+        <v>-15.88378842844975</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -2174,13 +2174,13 @@
         <v>-3.994646134946914</v>
       </c>
       <c r="E78">
-        <v>-22.06241950584506</v>
+        <v>-29.4803520169826</v>
       </c>
       <c r="F78">
-        <v>-2.720244383339498</v>
+        <v>-3.677289550122476</v>
       </c>
       <c r="G78">
-        <v>-10.08615748152738</v>
+        <v>-16.17786253343044</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -2197,13 +2197,13 @@
         <v>-3.760025835174294</v>
       </c>
       <c r="E79">
-        <v>-21.45871957893451</v>
+        <v>-29.67404617147568</v>
       </c>
       <c r="F79">
-        <v>-2.95335608252871</v>
+        <v>-3.773654358457545</v>
       </c>
       <c r="G79">
-        <v>-10.79408122909959</v>
+        <v>-15.95864813945652</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -2220,13 +2220,13 @@
         <v>-3.482191903081715</v>
       </c>
       <c r="E80">
-        <v>-21.73848870312839</v>
+        <v>-29.9202479820877</v>
       </c>
       <c r="F80">
-        <v>-2.848257796665925</v>
+        <v>-3.720998356131192</v>
       </c>
       <c r="G80">
-        <v>-10.06426153333064</v>
+        <v>-16.05995414350375</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -2243,13 +2243,13 @@
         <v>-3.167556013437608</v>
       </c>
       <c r="E81">
-        <v>-22.81605720714958</v>
+        <v>-29.93245674801238</v>
       </c>
       <c r="F81">
-        <v>-2.952235301432722</v>
+        <v>-3.815230118404052</v>
       </c>
       <c r="G81">
-        <v>-10.02663718327682</v>
+        <v>-16.05989951950236</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -2266,13 +2266,13 @@
         <v>-2.822846192820317</v>
       </c>
       <c r="E82">
-        <v>-23.97389744143074</v>
+        <v>-30.52212066973616</v>
       </c>
       <c r="F82">
-        <v>-2.672721773808293</v>
+        <v>-3.940767541563512</v>
       </c>
       <c r="G82">
-        <v>-10.20459555874034</v>
+        <v>-15.64686758165903</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -2289,13 +2289,13 @@
         <v>-2.454042125776828</v>
       </c>
       <c r="E83">
-        <v>-23.97969841663456</v>
+        <v>-31.22215482421188</v>
       </c>
       <c r="F83">
-        <v>-2.759976197447374</v>
+        <v>-4.096793026983007</v>
       </c>
       <c r="G83">
-        <v>-9.788791039007883</v>
+        <v>-15.5119429876605</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -2312,13 +2312,13 @@
         <v>-2.070162524084538</v>
       </c>
       <c r="E84">
-        <v>-24.68570109985239</v>
+        <v>-32.10583218512065</v>
       </c>
       <c r="F84">
-        <v>-3.275139541983191</v>
+        <v>-4.104098399108296</v>
       </c>
       <c r="G84">
-        <v>-10.15799631972956</v>
+        <v>-15.46657361631756</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -2335,13 +2335,13 @@
         <v>-1.684878065534671</v>
       </c>
       <c r="E85">
-        <v>-24.67386366879634</v>
+        <v>-31.87231689444113</v>
       </c>
       <c r="F85">
-        <v>-2.631311687342346</v>
+        <v>-4.064347532550156</v>
       </c>
       <c r="G85">
-        <v>-9.334349142286587</v>
+        <v>-15.18367591307744</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -2358,13 +2358,13 @@
         <v>-1.310848099043372</v>
       </c>
       <c r="E86">
-        <v>-25.88503121299183</v>
+        <v>-33.13354898302841</v>
       </c>
       <c r="F86">
-        <v>-2.72727556585446</v>
+        <v>-4.073288930295974</v>
       </c>
       <c r="G86">
-        <v>-9.379693684537985</v>
+        <v>-15.25842472080865</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -2381,13 +2381,13 @@
         <v>-0.9594285492307382</v>
       </c>
       <c r="E87">
-        <v>-28.39211669243634</v>
+        <v>-33.64361818135637</v>
       </c>
       <c r="F87">
-        <v>-3.765693747716642</v>
+        <v>-4.17692597606022</v>
       </c>
       <c r="G87">
-        <v>-8.38611289401868</v>
+        <v>-15.21298251746384</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -2404,13 +2404,13 @@
         <v>-0.6479388594161831</v>
       </c>
       <c r="E88">
-        <v>-28.72397232466644</v>
+        <v>-34.12142879509069</v>
       </c>
       <c r="F88">
-        <v>-3.255430196368383</v>
+        <v>-4.104389984434081</v>
       </c>
       <c r="G88">
-        <v>-8.799093518406144</v>
+        <v>-15.13141564119451</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -2427,13 +2427,13 @@
         <v>-0.3902576573564273</v>
       </c>
       <c r="E89">
-        <v>-30.33929032438748</v>
+        <v>-35.23341370157017</v>
       </c>
       <c r="F89">
-        <v>-3.278595490787671</v>
+        <v>-4.357011392694027</v>
       </c>
       <c r="G89">
-        <v>-8.935719732811865</v>
+        <v>-15.16185610742811</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -2450,13 +2450,13 @@
         <v>-0.1978535304023848</v>
       </c>
       <c r="E90">
-        <v>-31.2389939548094</v>
+        <v>-36.55786328730454</v>
       </c>
       <c r="F90">
-        <v>-3.062347695184652</v>
+        <v>-4.52097512293455</v>
       </c>
       <c r="G90">
-        <v>-8.637336952811815</v>
+        <v>-15.26679709047747</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -2473,13 +2473,13 @@
         <v>-0.08384359331429911</v>
       </c>
       <c r="E91">
-        <v>-31.23866564044384</v>
+        <v>-36.97360210781572</v>
       </c>
       <c r="F91">
-        <v>-3.056708998273796</v>
+        <v>-4.662143838984836</v>
       </c>
       <c r="G91">
-        <v>-8.697900072907242</v>
+        <v>-14.9316291837178</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -2496,13 +2496,13 @@
         <v>-0.06224676292635544</v>
       </c>
       <c r="E92">
-        <v>-33.43603746131877</v>
+        <v>-37.9985633292898</v>
       </c>
       <c r="F92">
-        <v>-3.487326680577687</v>
+        <v>-4.530113672122234</v>
       </c>
       <c r="G92">
-        <v>-9.077930837542338</v>
+        <v>-15.63745735596365</v>
       </c>
     </row>
     <row r="93" spans="1:7">
@@ -2519,13 +2519,13 @@
         <v>-0.141748072068057</v>
       </c>
       <c r="E93">
-        <v>-35.13831121893509</v>
+        <v>-39.49017021183229</v>
       </c>
       <c r="F93">
-        <v>-3.871716491600951</v>
+        <v>-4.69650783232257</v>
       </c>
       <c r="G93">
-        <v>-9.149077771726814</v>
+        <v>-15.39576435777808</v>
       </c>
     </row>
     <row r="94" spans="1:7">
@@ -2542,13 +2542,13 @@
         <v>-0.322927094518789</v>
       </c>
       <c r="E94">
-        <v>-35.99111344405957</v>
+        <v>-41.02652068180758</v>
       </c>
       <c r="F94">
-        <v>-3.526124096255205</v>
+        <v>-4.652124735247976</v>
       </c>
       <c r="G94">
-        <v>-10.20194381176339</v>
+        <v>-15.19345691987322</v>
       </c>
     </row>
     <row r="95" spans="1:7">
@@ -2565,13 +2565,13 @@
         <v>-0.6072355248166045</v>
       </c>
       <c r="E95">
-        <v>-37.44316410614506</v>
+        <v>-42.35814337037009</v>
       </c>
       <c r="F95">
-        <v>-3.461595932311929</v>
+        <v>-4.829292641889123</v>
       </c>
       <c r="G95">
-        <v>-9.648384181596313</v>
+        <v>-15.73854982982361</v>
       </c>
     </row>
     <row r="96" spans="1:7">
@@ -2588,13 +2588,13 @@
         <v>-0.9937560428607694</v>
       </c>
       <c r="E96">
-        <v>-39.12804852357193</v>
+        <v>-43.44678852181404</v>
       </c>
       <c r="F96">
-        <v>-3.961040177012224</v>
+        <v>-4.812595240150894</v>
       </c>
       <c r="G96">
-        <v>-9.467558873695781</v>
+        <v>-15.46912604692833</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -2611,13 +2611,13 @@
         <v>-1.462103834064417</v>
       </c>
       <c r="E97">
-        <v>-40.96835243317905</v>
+        <v>-45.04594213356469</v>
       </c>
       <c r="F97">
-        <v>-3.582241017590455</v>
+        <v>-5.070325190183904</v>
       </c>
       <c r="G97">
-        <v>-9.444136764005437</v>
+        <v>-15.80778988977747</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -2634,13 +2634,13 @@
         <v>-2.012521319132796</v>
       </c>
       <c r="E98">
-        <v>-42.75399992575059</v>
+        <v>-46.30400429034661</v>
       </c>
       <c r="F98">
-        <v>-4.300198642740425</v>
+        <v>-5.260484382803155</v>
       </c>
       <c r="G98">
-        <v>-10.98177591899411</v>
+        <v>-16.19467348367886</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -2657,13 +2657,13 @@
         <v>-2.609083310073109</v>
       </c>
       <c r="E99">
-        <v>-44.0000186059091</v>
+        <v>-47.81687915106613</v>
       </c>
       <c r="F99">
-        <v>-4.159828472866439</v>
+        <v>-5.135780297250912</v>
       </c>
       <c r="G99">
-        <v>-9.447245366266813</v>
+        <v>-16.22312596731612</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -2680,13 +2680,13 @@
         <v>-3.266096131902279</v>
       </c>
       <c r="E100">
-        <v>-45.99777982099992</v>
+        <v>-49.44542708760057</v>
       </c>
       <c r="F100">
-        <v>-3.785818105400253</v>
+        <v>-5.307447015970068</v>
       </c>
       <c r="G100">
-        <v>-10.42360138834529</v>
+        <v>-16.13839420951124</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -2703,13 +2703,13 @@
         <v>-3.909517199475924</v>
       </c>
       <c r="E101">
-        <v>-48.53836015844217</v>
+        <v>-50.69678597073263</v>
       </c>
       <c r="F101">
-        <v>-4.568273244899596</v>
+        <v>-5.623846915673756</v>
       </c>
       <c r="G101">
-        <v>-11.00231785406529</v>
+        <v>-16.65792308680738</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -2726,13 +2726,13 @@
         <v>-4.612871064531544</v>
       </c>
       <c r="E102">
-        <v>-50.66759089880518</v>
+        <v>-53.14313895314178</v>
       </c>
       <c r="F102">
-        <v>-4.513895895110226</v>
+        <v>-5.740080116164971</v>
       </c>
       <c r="G102">
-        <v>-10.50403771331296</v>
+        <v>-16.83172672761912</v>
       </c>
     </row>
   </sheetData>
